--- a/Apostas_Diarias/Apostas_20260402.xlsx
+++ b/Apostas_Diarias/Apostas_20260402.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_2B590F4F9526CFEC0500BE105E1510344D07F76D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047101D9-B164-4D23-9C34-123297D5ABFF}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_2B590F4F95C6450E9D00D5F050BAF8774001E589" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{296D3786-BF8F-48DC-8EC0-DF9E1993E17D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="33">
   <si>
     <t>Data</t>
   </si>
@@ -71,6 +71,42 @@
     <t>2026-04-02</t>
   </si>
   <si>
+    <t>P1 ⭐</t>
+  </si>
+  <si>
+    <t>10:15:00</t>
+  </si>
+  <si>
+    <t>SAUDI ARABIA 1</t>
+  </si>
+  <si>
+    <t>Al-Jndal x Jeddah Club</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
+    <t>14:35:00</t>
+  </si>
+  <si>
+    <t>Al-Zulfi SC x Al-Anwar Club</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>ARGENTINA 1</t>
+  </si>
+  <si>
+    <t>Tigre x Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
+    <t>Talleres x Boca Juniors</t>
+  </si>
+  <si>
     <t>P2</t>
   </si>
   <si>
@@ -83,13 +119,19 @@
     <t>Chapecoense x Atletico MG</t>
   </si>
   <si>
-    <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
     <t>21:30:00</t>
   </si>
   <si>
     <t>Red Bull Bragantino x Flamengo</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Lay_CS_1x0_B365</t>
+  </si>
+  <si>
+    <t>P4</t>
   </si>
 </sst>
 </file>
@@ -429,13 +471,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -499,10 +542,10 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="I2">
         <v>500</v>
@@ -513,7 +556,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>61.513157894736842</v>
+        <v>31.166666666666668</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -524,42 +567,405 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>500</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J12" si="0">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K12" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>58.4375</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G3">
+      <c r="G4">
+        <v>13.5</v>
+      </c>
+      <c r="H4">
+        <v>13.5</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>37.400000000000006</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5">
+        <v>9.4</v>
+      </c>
+      <c r="H5">
+        <v>9.4</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>55.654761904761905</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>8.6</v>
       </c>
-      <c r="H3">
+      <c r="H6">
         <v>8.6</v>
       </c>
-      <c r="I3">
-        <v>500</v>
-      </c>
-      <c r="J3" t="str">
-        <f>IF(L3=1,"GREEN","RED")</f>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
-      <c r="K3">
-        <f>IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+      <c r="K6">
+        <f t="shared" si="1"/>
         <v>61.513157894736842</v>
       </c>
-      <c r="L3">
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>11.5</v>
+      </c>
+      <c r="H7">
+        <v>11.5</v>
+      </c>
+      <c r="I7">
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>8.6</v>
+      </c>
+      <c r="H8">
+        <v>8.6</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>61.513157894736842</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="H9">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I9">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10">
+        <v>7.2</v>
+      </c>
+      <c r="H10">
+        <v>7.2</v>
+      </c>
+      <c r="I10">
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>75.403225806451616</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11">
+        <v>11</v>
+      </c>
+      <c r="I11">
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>46.75</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>7</v>
+      </c>
+      <c r="I12">
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>77.916666666666671</v>
+      </c>
+      <c r="L12">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K12">
+    <sortCondition ref="E2:E12"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>